--- a/Flag/Extrair DP/Planilha_FLAG.xlsx
+++ b/Flag/Extrair DP/Planilha_FLAG.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Anticoagulante Seguro</t>
+          <t>Emagrecimento</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>079833881</t>
+          <t>088206760</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>093127766</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>096353876</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>452147883</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>093636061</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>087729262</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>088988201</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Anticoagulante Seguro</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>074100532</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Anticoagulante Seguro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>777529505</t>
         </is>
       </c>
     </row>
